--- a/artfynd/A 2531-2024 artfynd.xlsx
+++ b/artfynd/A 2531-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2531-2024 artfynd.xlsx
+++ b/artfynd/A 2531-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,123 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4168686</v>
-      </c>
-      <c r="B3" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Bergsluttning 250 m S om gården Björnåsen, Boh</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>317867.9221627231</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6503806.215372269</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Sanne</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2000-06-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2000-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2531-2024 artfynd.xlsx
+++ b/artfynd/A 2531-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,123 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4168686</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95510</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lopplummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bergsluttning 250 m S om gården Björnåsen, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>317867.9221627231</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6503806.215372269</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sanne</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2000-06-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2000-06-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2531-2024 artfynd.xlsx
+++ b/artfynd/A 2531-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4215519</v>
+        <v>4985318</v>
       </c>
       <c r="B2" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergsluttning 250 m S om gården Björnåsen, Boh</t>
+          <t>Vid vägen 250 m V om gården Björnåsen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317867.9221627231</v>
+        <v>317696</v>
       </c>
       <c r="R2" t="n">
-        <v>6503806.215372269</v>
+        <v>6503974</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-06-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sanne, Berg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,35 +762,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Flora Bohuslän</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Flora Bohuslän</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4168686</v>
+        <v>5254108</v>
       </c>
       <c r="B3" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsluttning 250 m S om gården Björnåsen, Boh</t>
+          <t>Vid vägen 250 m V om gården Björnåsen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317867.9221627231</v>
+        <v>317696</v>
       </c>
       <c r="R3" t="n">
-        <v>6503806.215372269</v>
+        <v>6503974</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2000-06-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2000-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-06-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sanne, Berg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,20 +864,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Flora Bohuslän</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Flora Bohuslän</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 2531-2024 artfynd.xlsx
+++ b/artfynd/A 2531-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4985318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5254108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>